--- a/Spine_Projects/01_input_data/01_input_raw/Products/jet_fuel/Model_Data_Base_jet_fuel.xlsx
+++ b/Spine_Projects/01_input_data/01_input_raw/Products/jet_fuel/Model_Data_Base_jet_fuel.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://studentcbs-my.sharepoint.com/personal/djh_eco_cbs_dk/Documents/Documents/GitHub/Nord_H2ub/Spine_Projects/01_input_data/01_input_raw/Products/jet_fuel/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kar.eco\Documents\GitHub\Nord_H2ub\Spine_Projects\01_input_data\01_input_raw\Products\jet_fuel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="21" documentId="13_ncr:1_{384EF942-1BB3-4AF5-A4C8-1EAD5F73D2B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0CBDAA88-D274-4E38-B411-90287AD514EF}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F93305B2-7AB8-4BC2-A69D-68A8FC16139F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11620" activeTab="2" xr2:uid="{50334894-9481-4F8E-BD29-206032E10C62}"/>
+    <workbookView xWindow="25695" yWindow="0" windowWidth="26010" windowHeight="20985" activeTab="2" xr2:uid="{50334894-9481-4F8E-BD29-206032E10C62}"/>
   </bookViews>
   <sheets>
     <sheet name="Units" sheetId="1" r:id="rId1"/>
@@ -74,7 +74,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="230" uniqueCount="125">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="272" uniqueCount="134">
   <si>
     <t>Unit</t>
   </si>
@@ -449,6 +449,33 @@
   </si>
   <si>
     <t>initial_connections_invested_available</t>
+  </si>
+  <si>
+    <t>solar_plant_node</t>
+  </si>
+  <si>
+    <t>wind_onshore_plant_node</t>
+  </si>
+  <si>
+    <t>wind_offshore_plant_node</t>
+  </si>
+  <si>
+    <t>pl_wholesale_solar</t>
+  </si>
+  <si>
+    <t>pl_solar_PPA</t>
+  </si>
+  <si>
+    <t>pl_wholesale_wind_onshore</t>
+  </si>
+  <si>
+    <t>pl_wind_onshore_PPA</t>
+  </si>
+  <si>
+    <t>pl_wholesale_wind_offshore</t>
+  </si>
+  <si>
+    <t>pl_wind_offshore_PPA</t>
   </si>
 </sst>
 </file>
@@ -555,7 +582,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -568,6 +595,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -867,8 +895,8 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{EFFB7C99-360E-4E9C-9C4B-24063303FF25}" name="Table13" displayName="Table13" ref="A1:AA5" totalsRowShown="0">
-  <autoFilter ref="A1:AA5" xr:uid="{EFFB7C99-360E-4E9C-9C4B-24063303FF25}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{EFFB7C99-360E-4E9C-9C4B-24063303FF25}" name="Table13" displayName="Table13" ref="A1:AA11" totalsRowShown="0">
+  <autoFilter ref="A1:AA11" xr:uid="{EFFB7C99-360E-4E9C-9C4B-24063303FF25}"/>
   <tableColumns count="27">
     <tableColumn id="1" xr3:uid="{0B60459B-BFAA-433A-998B-57564CCEFAF1}" name="Connection"/>
     <tableColumn id="2" xr3:uid="{C0C61C1C-8F08-418C-94F7-C2BD6112A62E}" name="Object_type"/>
@@ -1233,13 +1261,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{576C757C-091A-46DF-949E-B17661031FDE}">
   <dimension ref="A1:T14"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="15.08984375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="19.6328125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="15.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="19.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1295,7 +1323,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="2" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>62</v>
       </c>
@@ -1303,12 +1331,12 @@
         <v>41</v>
       </c>
       <c r="C2" t="s">
-        <v>63</v>
+        <v>125</v>
       </c>
       <c r="P2" s="1"/>
       <c r="Q2" s="1"/>
     </row>
-    <row r="3" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>96</v>
       </c>
@@ -1316,12 +1344,12 @@
         <v>97</v>
       </c>
       <c r="C3" t="s">
-        <v>63</v>
+        <v>126</v>
       </c>
       <c r="P3" s="1"/>
       <c r="Q3" s="1"/>
     </row>
-    <row r="4" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>98</v>
       </c>
@@ -1329,12 +1357,12 @@
         <v>99</v>
       </c>
       <c r="C4" t="s">
-        <v>63</v>
+        <v>127</v>
       </c>
       <c r="P4" s="1"/>
       <c r="Q4" s="1"/>
     </row>
-    <row r="5" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>64</v>
       </c>
@@ -1356,7 +1384,7 @@
       <c r="P5" s="1"/>
       <c r="Q5" s="1"/>
     </row>
-    <row r="6" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>67</v>
       </c>
@@ -1369,7 +1397,7 @@
       <c r="P6" s="1"/>
       <c r="Q6" s="1"/>
     </row>
-    <row r="7" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>75</v>
       </c>
@@ -1382,7 +1410,7 @@
       <c r="P7" s="1"/>
       <c r="Q7" s="1"/>
     </row>
-    <row r="8" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
         <v>70</v>
       </c>
@@ -1395,7 +1423,7 @@
       <c r="P8" s="1"/>
       <c r="Q8" s="1"/>
     </row>
-    <row r="9" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>89</v>
       </c>
@@ -1411,7 +1439,7 @@
       <c r="P9" s="1"/>
       <c r="Q9" s="1"/>
     </row>
-    <row r="10" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
         <v>73</v>
       </c>
@@ -1430,7 +1458,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>117</v>
       </c>
@@ -1445,7 +1473,7 @@
       <c r="S11" s="1"/>
       <c r="T11" s="1"/>
     </row>
-    <row r="12" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A12" s="5" t="s">
         <v>100</v>
       </c>
@@ -1458,7 +1486,7 @@
       <c r="P12" s="1"/>
       <c r="Q12" s="1"/>
     </row>
-    <row r="13" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A13" s="6" t="s">
         <v>101</v>
       </c>
@@ -1471,7 +1499,7 @@
       <c r="P13" s="1"/>
       <c r="Q13" s="1"/>
     </row>
-    <row r="14" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A14" s="9" t="s">
         <v>116</v>
       </c>
@@ -1499,13 +1527,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8478C130-C296-4571-ABF4-62E91E9E2767}">
   <dimension ref="A1:Q14"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="15.08984375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="19.6328125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="15.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="19.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1558,7 +1586,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>62</v>
       </c>
@@ -1569,8 +1597,8 @@
       <c r="D2" s="2"/>
       <c r="E2" s="2"/>
       <c r="F2" s="2"/>
-      <c r="G2" s="2" t="s">
-        <v>63</v>
+      <c r="G2" t="s">
+        <v>125</v>
       </c>
       <c r="H2" s="2"/>
       <c r="I2" s="8"/>
@@ -1583,7 +1611,7 @@
       <c r="P2" s="8"/>
       <c r="Q2" s="8"/>
     </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
         <v>96</v>
       </c>
@@ -1594,8 +1622,8 @@
       <c r="D3" s="3"/>
       <c r="E3" s="3"/>
       <c r="F3" s="3"/>
-      <c r="G3" s="3" t="s">
-        <v>63</v>
+      <c r="G3" t="s">
+        <v>126</v>
       </c>
       <c r="H3" s="3"/>
       <c r="I3" s="3"/>
@@ -1608,7 +1636,7 @@
       <c r="P3" s="3"/>
       <c r="Q3" s="3"/>
     </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>98</v>
       </c>
@@ -1619,8 +1647,8 @@
       <c r="D4" s="2"/>
       <c r="E4" s="2"/>
       <c r="F4" s="2"/>
-      <c r="G4" s="2" t="s">
-        <v>63</v>
+      <c r="G4" t="s">
+        <v>127</v>
       </c>
       <c r="H4" s="2"/>
       <c r="I4" s="2"/>
@@ -1633,7 +1661,7 @@
       <c r="P4" s="2"/>
       <c r="Q4" s="2"/>
     </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
         <v>64</v>
       </c>
@@ -1668,7 +1696,7 @@
       <c r="P5" s="3"/>
       <c r="Q5" s="3"/>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>67</v>
       </c>
@@ -1701,7 +1729,7 @@
       <c r="P6" s="2"/>
       <c r="Q6" s="2"/>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>75</v>
       </c>
@@ -1738,7 +1766,7 @@
       <c r="P7" s="3"/>
       <c r="Q7" s="3"/>
     </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>70</v>
       </c>
@@ -1779,7 +1807,7 @@
       <c r="P8" s="2"/>
       <c r="Q8" s="2"/>
     </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>89</v>
       </c>
@@ -1812,7 +1840,7 @@
       <c r="P9" s="3"/>
       <c r="Q9" s="3"/>
     </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>100</v>
       </c>
@@ -1829,7 +1857,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>101</v>
       </c>
@@ -1858,7 +1886,7 @@
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
     </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>73</v>
       </c>
@@ -1905,7 +1933,7 @@
       </c>
       <c r="Q12" s="9"/>
     </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
         <v>117</v>
       </c>
@@ -1934,7 +1962,7 @@
       <c r="P13" s="3"/>
       <c r="Q13" s="3"/>
     </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A14" s="9" t="s">
         <v>116</v>
       </c>
@@ -1974,34 +2002,34 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C870BDA0-9E4C-481D-87BE-9D47789809C8}">
-  <dimension ref="A1:AA5"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:AA11"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="14.26953125" customWidth="1"/>
-    <col min="2" max="2" width="17.453125" bestFit="1" customWidth="1"/>
-    <col min="3" max="6" width="16.1796875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="35.1796875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="20.7265625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="17.453125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="20.7265625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="17.453125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="22.1796875" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="19.08984375" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="22.1796875" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="19.08984375" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="10.90625" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="15.6328125" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="17.1796875" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="18.81640625" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="17.1796875" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="11.81640625" bestFit="1" customWidth="1"/>
-    <col min="22" max="23" width="17.81640625" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="19.453125" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="36.54296875" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="24.26953125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14.28515625" customWidth="1"/>
+    <col min="2" max="2" width="17.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="6" width="16.140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="35.140625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="20.7109375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="17.42578125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="20.7109375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="17.42578125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="22.140625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="19.140625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="22.140625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="19.140625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="10.85546875" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="15.5703125" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="17.140625" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="18.85546875" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="17.140625" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="11.85546875" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="17.85546875" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="19.42578125" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="36.5703125" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="24.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>15</v>
       </c>
@@ -2084,7 +2112,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="2" spans="1:27" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>79</v>
       </c>
@@ -2143,7 +2171,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:27" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>81</v>
       </c>
@@ -2199,7 +2227,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:27" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
         <v>90</v>
       </c>
@@ -2225,7 +2253,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:27" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>83</v>
       </c>
@@ -2260,6 +2288,300 @@
         <v>46</v>
       </c>
       <c r="AA5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>128</v>
+      </c>
+      <c r="B6" t="s">
+        <v>44</v>
+      </c>
+      <c r="C6" t="s">
+        <v>80</v>
+      </c>
+      <c r="D6" t="s">
+        <v>125</v>
+      </c>
+      <c r="E6" t="s">
+        <v>125</v>
+      </c>
+      <c r="F6" s="10" t="s">
+        <v>80</v>
+      </c>
+      <c r="G6" t="s">
+        <v>48</v>
+      </c>
+      <c r="H6">
+        <v>1000</v>
+      </c>
+      <c r="I6">
+        <v>1000</v>
+      </c>
+      <c r="J6">
+        <v>1000</v>
+      </c>
+      <c r="K6">
+        <v>1000</v>
+      </c>
+      <c r="L6">
+        <v>1000</v>
+      </c>
+      <c r="M6">
+        <v>1000</v>
+      </c>
+      <c r="N6">
+        <v>1000</v>
+      </c>
+      <c r="O6">
+        <v>1000</v>
+      </c>
+      <c r="R6">
+        <v>1</v>
+      </c>
+      <c r="T6">
+        <v>1</v>
+      </c>
+      <c r="Z6" t="s">
+        <v>46</v>
+      </c>
+      <c r="AA6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>129</v>
+      </c>
+      <c r="B7" t="s">
+        <v>44</v>
+      </c>
+      <c r="C7" t="s">
+        <v>125</v>
+      </c>
+      <c r="E7" t="s">
+        <v>63</v>
+      </c>
+      <c r="F7" s="10"/>
+      <c r="G7" t="s">
+        <v>48</v>
+      </c>
+      <c r="H7">
+        <v>1000</v>
+      </c>
+      <c r="I7">
+        <v>1000</v>
+      </c>
+      <c r="L7">
+        <v>1000</v>
+      </c>
+      <c r="M7">
+        <v>1000</v>
+      </c>
+      <c r="T7">
+        <v>1</v>
+      </c>
+      <c r="Z7" t="s">
+        <v>46</v>
+      </c>
+      <c r="AA7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>130</v>
+      </c>
+      <c r="B8" t="s">
+        <v>44</v>
+      </c>
+      <c r="C8" t="s">
+        <v>80</v>
+      </c>
+      <c r="D8" t="s">
+        <v>126</v>
+      </c>
+      <c r="E8" t="s">
+        <v>126</v>
+      </c>
+      <c r="F8" s="10" t="s">
+        <v>80</v>
+      </c>
+      <c r="G8" t="s">
+        <v>48</v>
+      </c>
+      <c r="H8">
+        <v>1000</v>
+      </c>
+      <c r="I8">
+        <v>1000</v>
+      </c>
+      <c r="J8">
+        <v>1000</v>
+      </c>
+      <c r="K8">
+        <v>1000</v>
+      </c>
+      <c r="L8">
+        <v>1000</v>
+      </c>
+      <c r="M8">
+        <v>1000</v>
+      </c>
+      <c r="N8">
+        <v>1000</v>
+      </c>
+      <c r="O8">
+        <v>1000</v>
+      </c>
+      <c r="R8">
+        <v>1</v>
+      </c>
+      <c r="T8">
+        <v>1</v>
+      </c>
+      <c r="Z8" t="s">
+        <v>46</v>
+      </c>
+      <c r="AA8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>131</v>
+      </c>
+      <c r="B9" t="s">
+        <v>44</v>
+      </c>
+      <c r="C9" t="s">
+        <v>126</v>
+      </c>
+      <c r="E9" t="s">
+        <v>63</v>
+      </c>
+      <c r="F9" s="10"/>
+      <c r="G9" t="s">
+        <v>48</v>
+      </c>
+      <c r="H9">
+        <v>1000</v>
+      </c>
+      <c r="I9">
+        <v>1000</v>
+      </c>
+      <c r="L9">
+        <v>1000</v>
+      </c>
+      <c r="M9">
+        <v>1000</v>
+      </c>
+      <c r="T9">
+        <v>1</v>
+      </c>
+      <c r="Z9" t="s">
+        <v>46</v>
+      </c>
+      <c r="AA9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>132</v>
+      </c>
+      <c r="B10" t="s">
+        <v>44</v>
+      </c>
+      <c r="C10" t="s">
+        <v>80</v>
+      </c>
+      <c r="D10" t="s">
+        <v>127</v>
+      </c>
+      <c r="E10" t="s">
+        <v>127</v>
+      </c>
+      <c r="F10" s="10" t="s">
+        <v>80</v>
+      </c>
+      <c r="G10" t="s">
+        <v>48</v>
+      </c>
+      <c r="H10">
+        <v>1000</v>
+      </c>
+      <c r="I10">
+        <v>1000</v>
+      </c>
+      <c r="J10">
+        <v>1000</v>
+      </c>
+      <c r="K10">
+        <v>1000</v>
+      </c>
+      <c r="L10">
+        <v>1000</v>
+      </c>
+      <c r="M10">
+        <v>1000</v>
+      </c>
+      <c r="N10">
+        <v>1000</v>
+      </c>
+      <c r="O10">
+        <v>1000</v>
+      </c>
+      <c r="R10">
+        <v>1</v>
+      </c>
+      <c r="T10">
+        <v>1</v>
+      </c>
+      <c r="Z10" t="s">
+        <v>46</v>
+      </c>
+      <c r="AA10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>133</v>
+      </c>
+      <c r="B11" t="s">
+        <v>44</v>
+      </c>
+      <c r="C11" t="s">
+        <v>127</v>
+      </c>
+      <c r="E11" t="s">
+        <v>63</v>
+      </c>
+      <c r="F11" s="10"/>
+      <c r="G11" t="s">
+        <v>48</v>
+      </c>
+      <c r="H11">
+        <v>1000</v>
+      </c>
+      <c r="I11">
+        <v>1000</v>
+      </c>
+      <c r="L11">
+        <v>1000</v>
+      </c>
+      <c r="M11">
+        <v>1000</v>
+      </c>
+      <c r="T11">
+        <v>1</v>
+      </c>
+      <c r="Z11" t="s">
+        <v>46</v>
+      </c>
+      <c r="AA11">
         <v>1</v>
       </c>
     </row>
@@ -2275,20 +2597,20 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{981CFA5E-60F3-446F-A856-2FA65B76879A}">
   <dimension ref="A1:K3"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="10.08984375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.6328125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.54296875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="16.6328125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="15.81640625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="15.81640625" customWidth="1"/>
+    <col min="1" max="1" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.5703125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="16.5703125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15.85546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="15.85546875" customWidth="1"/>
     <col min="7" max="7" width="9" customWidth="1"/>
     <col min="8" max="8" width="11" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="11.26953125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="11.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>19</v>
       </c>
@@ -2323,7 +2645,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>82</v>
       </c>
@@ -2349,7 +2671,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
         <v>85</v>
       </c>
@@ -2398,102 +2720,102 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4F682EA3-CCEB-45E2-AC25-979810840C6C}">
   <dimension ref="A1:A19"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="19.6328125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="19.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>95</v>
       </c>

--- a/Spine_Projects/01_input_data/01_input_raw/Products/jet_fuel/Model_Data_Base_jet_fuel.xlsx
+++ b/Spine_Projects/01_input_data/01_input_raw/Products/jet_fuel/Model_Data_Base_jet_fuel.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kar.eco\Documents\GitHub\Nord_H2ub\Spine_Projects\01_input_data\01_input_raw\Products\jet_fuel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F93305B2-7AB8-4BC2-A69D-68A8FC16139F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2224631A-0689-4B3D-A1E5-2107ECC324E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="25695" yWindow="0" windowWidth="26010" windowHeight="20985" activeTab="2" xr2:uid="{50334894-9481-4F8E-BD29-206032E10C62}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" activeTab="4" xr2:uid="{50334894-9481-4F8E-BD29-206032E10C62}"/>
   </bookViews>
   <sheets>
     <sheet name="Units" sheetId="1" r:id="rId1"/>
@@ -74,7 +74,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="272" uniqueCount="134">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="264" uniqueCount="133">
   <si>
     <t>Unit</t>
   </si>
@@ -352,12 +352,6 @@
     <t>initial_units_on</t>
   </si>
   <si>
-    <t>heat_low</t>
-  </si>
-  <si>
-    <t>heat_high</t>
-  </si>
-  <si>
     <t>Auxilliary</t>
   </si>
   <si>
@@ -427,9 +421,6 @@
     <t>power_steam</t>
   </si>
   <si>
-    <t>heat_recovery</t>
-  </si>
-  <si>
     <t>Relation_In1_In3</t>
   </si>
   <si>
@@ -476,13 +467,19 @@
   </si>
   <si>
     <t>pl_wind_offshore_PPA</t>
+  </si>
+  <si>
+    <t>excess_heat</t>
+  </si>
+  <si>
+    <t>heat</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -492,6 +489,13 @@
     </font>
     <font>
       <sz val="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -517,7 +521,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="6">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -534,30 +538,6 @@
       <bottom style="thin">
         <color theme="4" tint="0.39997558519241921"/>
       </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color theme="4" tint="0.39997558519241921"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color theme="4" tint="0.39997558519241921"/>
-      </top>
-      <bottom style="thin">
-        <color theme="4" tint="0.39997558519241921"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color theme="4" tint="0.39997558519241921"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color theme="4" tint="0.39997558519241921"/>
-      </top>
-      <bottom/>
       <diagonal/>
     </border>
     <border>
@@ -582,7 +562,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -590,17 +570,112 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="19">
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
     <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
     </dxf>
@@ -611,104 +686,6 @@
           <bgColor auto="1"/>
         </patternFill>
       </fill>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right/>
-        <top style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right/>
-        <top style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right/>
-        <top style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right/>
-        <top style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right/>
-        <top style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right/>
-        <top style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right/>
-        <top style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
     </dxf>
     <dxf>
       <border diagonalUp="0" diagonalDown="0">
@@ -842,8 +819,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{0333CFC6-D067-4B12-B0A1-83E429D32CCD}" name="Table1" displayName="Table1" ref="A1:R14" totalsRowShown="0">
-  <autoFilter ref="A1:R14" xr:uid="{0333CFC6-D067-4B12-B0A1-83E429D32CCD}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{0333CFC6-D067-4B12-B0A1-83E429D32CCD}" name="Table1" displayName="Table1" ref="A1:R13" totalsRowShown="0">
+  <autoFilter ref="A1:R13" xr:uid="{0333CFC6-D067-4B12-B0A1-83E429D32CCD}"/>
   <tableColumns count="18">
     <tableColumn id="1" xr3:uid="{D347015F-CF17-4A9D-8294-ADF748DF1773}" name="Unit"/>
     <tableColumn id="2" xr3:uid="{D82A47BB-4363-4E36-A8AE-65EDC2C013A4}" name="Object_type"/>
@@ -869,26 +846,26 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{12FAA58E-4414-4B31-B756-3FD9A04CACB5}" name="Table16" displayName="Table16" ref="A1:Q14" totalsRowShown="0">
-  <autoFilter ref="A1:Q14" xr:uid="{0333CFC6-D067-4B12-B0A1-83E429D32CCD}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{12FAA58E-4414-4B31-B756-3FD9A04CACB5}" name="Table16" displayName="Table16" ref="A1:Q13" totalsRowShown="0">
+  <autoFilter ref="A1:Q13" xr:uid="{0333CFC6-D067-4B12-B0A1-83E429D32CCD}"/>
   <tableColumns count="17">
     <tableColumn id="1" xr3:uid="{CD5761E6-0259-4D3B-B945-2F2B9275A761}" name="Unit"/>
     <tableColumn id="2" xr3:uid="{8206E937-98CA-48B8-8ECF-A8CC8CEA0E7A}" name="Object_type"/>
-    <tableColumn id="3" xr3:uid="{25658B53-E729-4F77-A87A-2C1AA31D180F}" name="Input1" dataDxfId="16"/>
-    <tableColumn id="4" xr3:uid="{C20E16FC-DEE5-46FF-98E7-EC2B1178D89F}" name="Input2" dataDxfId="15"/>
-    <tableColumn id="13" xr3:uid="{C4257F9B-BEBE-4928-A299-FA13BAF91F57}" name="Input3" dataDxfId="14"/>
-    <tableColumn id="14" xr3:uid="{E33FDA0D-66C9-4616-8A81-6F5E0E166ED4}" name="Input4" dataDxfId="13"/>
-    <tableColumn id="5" xr3:uid="{901F195D-0BA8-4EDC-88F0-75A5DF763740}" name="Output1" dataDxfId="12"/>
-    <tableColumn id="6" xr3:uid="{0D5DCA48-4EAB-497A-B34F-5091694CCF48}" name="Output2" dataDxfId="11"/>
-    <tableColumn id="15" xr3:uid="{E758FC30-F120-4234-A984-DD9BB9F5CBE5}" name="Output3" dataDxfId="10"/>
-    <tableColumn id="16" xr3:uid="{85570B5D-60DB-4C61-80EB-881EDB346388}" name="Output4" dataDxfId="9"/>
-    <tableColumn id="10" xr3:uid="{40961C24-C288-48FE-96C9-C696058F1146}" name="Relation_In1_In2" dataDxfId="8"/>
-    <tableColumn id="7" xr3:uid="{E93572D0-6388-4D7C-A2BF-3805225F4F50}" name="Relation_In1_In3" dataDxfId="7"/>
-    <tableColumn id="8" xr3:uid="{BAF59A78-842A-475C-B900-52E45F0F2C02}" name="Relation_In1_In4" dataDxfId="6"/>
-    <tableColumn id="11" xr3:uid="{63A0B53D-07BC-4C95-B97C-243557E4A128}" name="Relation_In1_Out1" dataDxfId="5"/>
-    <tableColumn id="25" xr3:uid="{44B35FDD-04C5-401A-9765-766FCD023027}" name="Relation_Out1_Out2" dataDxfId="4"/>
-    <tableColumn id="9" xr3:uid="{3E00680F-559F-4DED-989F-C435D3C0AEC7}" name="Relation_Out1_Out3" dataDxfId="3"/>
-    <tableColumn id="12" xr3:uid="{17E13652-ACBE-480B-A89B-1AB97BFEAE60}" name="Relation_Out1_Out4" dataDxfId="2"/>
+    <tableColumn id="3" xr3:uid="{25658B53-E729-4F77-A87A-2C1AA31D180F}" name="Input1" dataDxfId="6"/>
+    <tableColumn id="4" xr3:uid="{C20E16FC-DEE5-46FF-98E7-EC2B1178D89F}" name="Input2" dataDxfId="5"/>
+    <tableColumn id="13" xr3:uid="{C4257F9B-BEBE-4928-A299-FA13BAF91F57}" name="Input3" dataDxfId="4"/>
+    <tableColumn id="14" xr3:uid="{E33FDA0D-66C9-4616-8A81-6F5E0E166ED4}" name="Input4" dataDxfId="3"/>
+    <tableColumn id="5" xr3:uid="{901F195D-0BA8-4EDC-88F0-75A5DF763740}" name="Output1" dataDxfId="2"/>
+    <tableColumn id="6" xr3:uid="{0D5DCA48-4EAB-497A-B34F-5091694CCF48}" name="Output2" dataDxfId="1"/>
+    <tableColumn id="15" xr3:uid="{E758FC30-F120-4234-A984-DD9BB9F5CBE5}" name="Output3" dataDxfId="0"/>
+    <tableColumn id="16" xr3:uid="{85570B5D-60DB-4C61-80EB-881EDB346388}" name="Output4" dataDxfId="16"/>
+    <tableColumn id="10" xr3:uid="{40961C24-C288-48FE-96C9-C696058F1146}" name="Relation_In1_In2" dataDxfId="15"/>
+    <tableColumn id="7" xr3:uid="{E93572D0-6388-4D7C-A2BF-3805225F4F50}" name="Relation_In1_In3" dataDxfId="14"/>
+    <tableColumn id="8" xr3:uid="{BAF59A78-842A-475C-B900-52E45F0F2C02}" name="Relation_In1_In4" dataDxfId="13"/>
+    <tableColumn id="11" xr3:uid="{63A0B53D-07BC-4C95-B97C-243557E4A128}" name="Relation_In1_Out1" dataDxfId="12"/>
+    <tableColumn id="25" xr3:uid="{44B35FDD-04C5-401A-9765-766FCD023027}" name="Relation_Out1_Out2" dataDxfId="11"/>
+    <tableColumn id="9" xr3:uid="{3E00680F-559F-4DED-989F-C435D3C0AEC7}" name="Relation_Out1_Out3" dataDxfId="10"/>
+    <tableColumn id="12" xr3:uid="{17E13652-ACBE-480B-A89B-1AB97BFEAE60}" name="Relation_Out1_Out4" dataDxfId="9"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -903,7 +880,7 @@
     <tableColumn id="3" xr3:uid="{BC9D86F7-8FDE-4FAF-A6B2-8BF7829723EF}" name="Input1"/>
     <tableColumn id="4" xr3:uid="{31F6D71E-306D-4146-A535-A6A629EBE2DC}" name="Input2"/>
     <tableColumn id="5" xr3:uid="{E176ABAF-D150-4E6A-8921-E24FCEB64CEB}" name="Output1"/>
-    <tableColumn id="22" xr3:uid="{EB53F534-595A-4E1E-82EE-E811ECDB4974}" name="Output2" dataDxfId="1"/>
+    <tableColumn id="22" xr3:uid="{EB53F534-595A-4E1E-82EE-E811ECDB4974}" name="Output2" dataDxfId="8"/>
     <tableColumn id="6" xr3:uid="{C9818184-D13F-4AF4-AE3A-C64F072A0385}" name="Connection_type"/>
     <tableColumn id="15" xr3:uid="{52C8ADC6-49B2-4339-A761-5E82E904E3A6}" name="Cap_Input1_existing"/>
     <tableColumn id="14" xr3:uid="{F6461E15-EE92-48B4-8879-9BDE3EBAAA17}" name="Cap_Input1_max"/>
@@ -934,7 +911,7 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{070C7B69-9214-47B9-93F0-C6C6118ED7CC}" name="Table134" displayName="Table134" ref="A1:K5" totalsRowShown="0">
   <autoFilter ref="A1:K5" xr:uid="{070C7B69-9214-47B9-93F0-C6C6118ED7CC}"/>
   <tableColumns count="11">
-    <tableColumn id="1" xr3:uid="{59CF1CEF-E7FA-4B7F-9443-D4A6EAAB7A8F}" name="Storage" dataDxfId="0"/>
+    <tableColumn id="1" xr3:uid="{59CF1CEF-E7FA-4B7F-9443-D4A6EAAB7A8F}" name="Storage" dataDxfId="7"/>
     <tableColumn id="4" xr3:uid="{AEAA1B51-84C1-491F-81D5-7757B30BDCCD}" name="Object_type"/>
     <tableColumn id="6" xr3:uid="{FA5F8582-61FC-4A96-9E8D-E08E92F1962D}" name="value_before"/>
     <tableColumn id="2" xr3:uid="{1FB70133-79C8-41A8-BCD5-AC8AA5856E5B}" name="has_state"/>
@@ -1260,14 +1237,30 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{576C757C-091A-46DF-949E-B17661031FDE}">
-  <dimension ref="A1:T14"/>
+  <dimension ref="A1:R13"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="15.140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="19.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="15.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="20.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="25.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="18.140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="18" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.85546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15.85546875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="18.42578125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="15.140625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="17.85546875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="15.7109375" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="11.42578125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="11.7109375" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="21.140625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="19.7109375" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="10.5703125" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="17.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1275,7 +1268,7 @@
         <v>34</v>
       </c>
       <c r="C1" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="D1" t="s">
         <v>36</v>
@@ -1284,16 +1277,16 @@
         <v>33</v>
       </c>
       <c r="F1" t="s">
+        <v>109</v>
+      </c>
+      <c r="G1" t="s">
+        <v>110</v>
+      </c>
+      <c r="H1" t="s">
         <v>111</v>
       </c>
-      <c r="G1" t="s">
+      <c r="I1" t="s">
         <v>112</v>
-      </c>
-      <c r="H1" t="s">
-        <v>113</v>
-      </c>
-      <c r="I1" t="s">
-        <v>114</v>
       </c>
       <c r="J1" t="s">
         <v>87</v>
@@ -1311,7 +1304,7 @@
         <v>27</v>
       </c>
       <c r="O1" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="P1" t="s">
         <v>38</v>
@@ -1323,7 +1316,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="2" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>62</v>
       </c>
@@ -1331,38 +1324,38 @@
         <v>41</v>
       </c>
       <c r="C2" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="P2" s="1"/>
       <c r="Q2" s="1"/>
     </row>
-    <row r="3" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="B3" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="C3" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="P3" s="1"/>
       <c r="Q3" s="1"/>
     </row>
-    <row r="4" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="B4" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="C4" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="P4" s="1"/>
       <c r="Q4" s="1"/>
     </row>
-    <row r="5" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>64</v>
       </c>
@@ -1384,7 +1377,7 @@
       <c r="P5" s="1"/>
       <c r="Q5" s="1"/>
     </row>
-    <row r="6" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>67</v>
       </c>
@@ -1397,7 +1390,7 @@
       <c r="P6" s="1"/>
       <c r="Q6" s="1"/>
     </row>
-    <row r="7" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>75</v>
       </c>
@@ -1410,7 +1403,7 @@
       <c r="P7" s="1"/>
       <c r="Q7" s="1"/>
     </row>
-    <row r="8" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
         <v>70</v>
       </c>
@@ -1423,7 +1416,7 @@
       <c r="P8" s="1"/>
       <c r="Q8" s="1"/>
     </row>
-    <row r="9" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>89</v>
       </c>
@@ -1439,7 +1432,7 @@
       <c r="P9" s="1"/>
       <c r="Q9" s="1"/>
     </row>
-    <row r="10" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
         <v>73</v>
       </c>
@@ -1450,7 +1443,7 @@
         <v>74</v>
       </c>
       <c r="E10" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="P10" s="1"/>
       <c r="Q10" s="1"/>
@@ -1458,62 +1451,47 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>117</v>
+        <v>98</v>
       </c>
       <c r="B11" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="C11" t="s">
-        <v>93</v>
+        <v>65</v>
       </c>
       <c r="P11" s="1"/>
       <c r="Q11" s="1"/>
-      <c r="S11" s="1"/>
-      <c r="T11" s="1"/>
-    </row>
-    <row r="12" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A12" s="5" t="s">
-        <v>100</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>94</v>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>99</v>
+      </c>
+      <c r="B12" t="s">
+        <v>92</v>
       </c>
       <c r="C12" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="P12" s="1"/>
       <c r="Q12" s="1"/>
     </row>
-    <row r="13" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A13" s="6" t="s">
-        <v>101</v>
-      </c>
-      <c r="B13" s="7" t="s">
-        <v>94</v>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>114</v>
+      </c>
+      <c r="B13" t="s">
+        <v>92</v>
       </c>
       <c r="C13" t="s">
-        <v>68</v>
-      </c>
-      <c r="P13" s="1"/>
-      <c r="Q13" s="1"/>
-    </row>
-    <row r="14" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A14" s="9" t="s">
-        <v>116</v>
-      </c>
-      <c r="B14" s="9" t="s">
-        <v>94</v>
-      </c>
-      <c r="C14" s="9" t="s">
         <v>63</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="P2:P9 S11" xr:uid="{30166407-D40D-4A67-99C1-251D943081A2}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="P2:P9" xr:uid="{30166407-D40D-4A67-99C1-251D943081A2}">
       <formula1>"h, D, W, M, Q, Y"</formula1>
     </dataValidation>
   </dataValidations>
@@ -1526,11 +1504,21 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8478C130-C296-4571-ABF4-62E91E9E2767}">
-  <dimension ref="A1:Q14"/>
+  <dimension ref="A1:Q13"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="15.140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="19.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="15.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="20.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.28515625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.85546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="9" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="25.7109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="11.85546875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="10.5703125" bestFit="1" customWidth="1"/>
+    <col min="11" max="13" width="18.28515625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="20" bestFit="1" customWidth="1"/>
+    <col min="15" max="17" width="21.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:17" x14ac:dyDescent="0.25">
@@ -1547,10 +1535,10 @@
         <v>2</v>
       </c>
       <c r="E1" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="F1" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="G1" t="s">
         <v>3</v>
@@ -1559,31 +1547,31 @@
         <v>4</v>
       </c>
       <c r="I1" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="J1" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="K1" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="L1" t="s">
+        <v>115</v>
+      </c>
+      <c r="M1" t="s">
+        <v>116</v>
+      </c>
+      <c r="N1" t="s">
+        <v>119</v>
+      </c>
+      <c r="O1" t="s">
+        <v>102</v>
+      </c>
+      <c r="P1" t="s">
+        <v>117</v>
+      </c>
+      <c r="Q1" t="s">
         <v>118</v>
-      </c>
-      <c r="M1" t="s">
-        <v>119</v>
-      </c>
-      <c r="N1" t="s">
-        <v>122</v>
-      </c>
-      <c r="O1" t="s">
-        <v>104</v>
-      </c>
-      <c r="P1" t="s">
-        <v>120</v>
-      </c>
-      <c r="Q1" t="s">
-        <v>121</v>
       </c>
     </row>
     <row r="2" spans="1:17" x14ac:dyDescent="0.25">
@@ -1598,32 +1586,32 @@
       <c r="E2" s="2"/>
       <c r="F2" s="2"/>
       <c r="G2" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="H2" s="2"/>
-      <c r="I2" s="8"/>
-      <c r="J2" s="8"/>
-      <c r="K2" s="8"/>
-      <c r="L2" s="8"/>
-      <c r="M2" s="8"/>
-      <c r="N2" s="8"/>
-      <c r="O2" s="8"/>
-      <c r="P2" s="8"/>
-      <c r="Q2" s="8"/>
+      <c r="I2" s="5"/>
+      <c r="J2" s="5"/>
+      <c r="K2" s="5"/>
+      <c r="L2" s="5"/>
+      <c r="M2" s="5"/>
+      <c r="N2" s="5"/>
+      <c r="O2" s="5"/>
+      <c r="P2" s="5"/>
+      <c r="Q2" s="5"/>
     </row>
     <row r="3" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="C3" s="3"/>
       <c r="D3" s="3"/>
       <c r="E3" s="3"/>
       <c r="F3" s="3"/>
       <c r="G3" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="H3" s="3"/>
       <c r="I3" s="3"/>
@@ -1638,17 +1626,17 @@
     </row>
     <row r="4" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="B4" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" s="2"/>
       <c r="E4" s="2"/>
       <c r="F4" s="2"/>
       <c r="G4" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="H4" s="2"/>
       <c r="I4" s="2"/>
@@ -1680,7 +1668,7 @@
         <v>66</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>92</v>
+        <v>131</v>
       </c>
       <c r="I5" s="3"/>
       <c r="J5" s="3"/>
@@ -1815,7 +1803,7 @@
         <v>42</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="D9" s="3" t="s">
         <v>65</v>
@@ -1842,13 +1830,13 @@
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
+        <v>98</v>
+      </c>
+      <c r="B10" t="s">
+        <v>92</v>
+      </c>
+      <c r="C10" s="3" t="s">
         <v>100</v>
-      </c>
-      <c r="B10" t="s">
-        <v>94</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>102</v>
       </c>
       <c r="G10" s="3" t="s">
         <v>65</v>
@@ -1859,13 +1847,13 @@
     </row>
     <row r="11" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
+        <v>99</v>
+      </c>
+      <c r="B11" t="s">
+        <v>92</v>
+      </c>
+      <c r="C11" s="3" t="s">
         <v>101</v>
-      </c>
-      <c r="B11" t="s">
-        <v>94</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>103</v>
       </c>
       <c r="D11" s="3"/>
       <c r="E11" s="3"/>
@@ -1893,61 +1881,59 @@
       <c r="B12" t="s">
         <v>58</v>
       </c>
-      <c r="C12" s="9" t="s">
+      <c r="C12" s="6" t="s">
         <v>66</v>
       </c>
       <c r="D12" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="E12" s="9" t="s">
+      <c r="E12" s="6" t="s">
         <v>71</v>
       </c>
-      <c r="F12" s="9"/>
-      <c r="G12" s="9" t="s">
+      <c r="F12" s="6"/>
+      <c r="G12" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="H12" s="9" t="s">
+      <c r="H12" s="6" t="s">
         <v>65</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="J12" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="J12" s="2"/>
+      <c r="K12" s="6">
+        <v>42.75</v>
+      </c>
+      <c r="L12" s="6">
+        <v>1.6132075471698113</v>
+      </c>
+      <c r="M12" s="6"/>
+      <c r="N12" s="6">
+        <v>1.6285714285714283</v>
+      </c>
+      <c r="O12" s="6">
+        <v>6.7340067340067344</v>
+      </c>
+      <c r="P12" s="7">
+        <v>5.5096418732782366</v>
+      </c>
+      <c r="Q12" s="6"/>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>114</v>
+      </c>
+      <c r="B13" t="s">
         <v>92</v>
       </c>
-      <c r="K12" s="9">
-        <v>42.75</v>
-      </c>
-      <c r="L12" s="9">
-        <v>1.6132075471698113</v>
-      </c>
-      <c r="M12" s="9"/>
-      <c r="N12" s="9">
-        <v>1.6285714285714283</v>
-      </c>
-      <c r="O12" s="9">
-        <v>6.7340067340067344</v>
-      </c>
-      <c r="P12" s="9">
-        <v>5.5096418732782366</v>
-      </c>
-      <c r="Q12" s="9"/>
-    </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A13" s="3" t="s">
-        <v>117</v>
-      </c>
-      <c r="B13" s="3" t="s">
-        <v>94</v>
-      </c>
       <c r="C13" s="3" t="s">
-        <v>93</v>
+        <v>63</v>
       </c>
       <c r="D13" s="3"/>
       <c r="E13" s="3"/>
       <c r="F13" s="3"/>
       <c r="G13" s="3" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="H13" s="3"/>
       <c r="I13" s="3"/>
@@ -1956,46 +1942,18 @@
       <c r="L13" s="3"/>
       <c r="M13" s="3"/>
       <c r="N13" s="3">
-        <v>1.1883541295306002</v>
+        <v>1</v>
       </c>
       <c r="O13" s="3"/>
       <c r="P13" s="3"/>
       <c r="Q13" s="3"/>
     </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A14" s="9" t="s">
-        <v>116</v>
-      </c>
-      <c r="B14" s="9" t="s">
-        <v>94</v>
-      </c>
-      <c r="C14" s="9" t="s">
-        <v>63</v>
-      </c>
-      <c r="D14" s="9"/>
-      <c r="E14" s="9"/>
-      <c r="F14" s="9"/>
-      <c r="G14" s="9" t="s">
-        <v>116</v>
-      </c>
-      <c r="H14" s="9"/>
-      <c r="I14" s="9"/>
-      <c r="J14" s="9"/>
-      <c r="K14" s="9"/>
-      <c r="L14" s="9"/>
-      <c r="M14" s="9"/>
-      <c r="N14" s="9">
-        <v>1</v>
-      </c>
-      <c r="O14" s="9"/>
-      <c r="P14" s="9"/>
-      <c r="Q14" s="9"/>
-    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <tableParts count="1">
-    <tablePart r:id="rId1"/>
+    <tablePart r:id="rId2"/>
   </tableParts>
 </worksheet>
 </file>
@@ -2005,10 +1963,11 @@
   <dimension ref="A1:AA11"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="14.28515625" customWidth="1"/>
-    <col min="2" max="2" width="17.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="6" width="16.140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="35.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="27.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="5" width="25.7109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="17" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="36.85546875" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="20.7109375" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="17.42578125" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="20.7109375" bestFit="1" customWidth="1"/>
@@ -2109,7 +2068,7 @@
         <v>35</v>
       </c>
       <c r="AA1" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
     </row>
     <row r="2" spans="1:27" x14ac:dyDescent="0.25">
@@ -2261,7 +2220,7 @@
         <v>50</v>
       </c>
       <c r="C5" t="s">
-        <v>92</v>
+        <v>132</v>
       </c>
       <c r="E5" t="s">
         <v>84</v>
@@ -2293,7 +2252,7 @@
     </row>
     <row r="6" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="B6" t="s">
         <v>44</v>
@@ -2302,12 +2261,12 @@
         <v>80</v>
       </c>
       <c r="D6" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="E6" t="s">
-        <v>125</v>
-      </c>
-      <c r="F6" s="10" t="s">
+        <v>122</v>
+      </c>
+      <c r="F6" t="s">
         <v>80</v>
       </c>
       <c r="G6" t="s">
@@ -2352,18 +2311,17 @@
     </row>
     <row r="7" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="B7" t="s">
         <v>44</v>
       </c>
       <c r="C7" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="E7" t="s">
         <v>63</v>
       </c>
-      <c r="F7" s="10"/>
       <c r="G7" t="s">
         <v>48</v>
       </c>
@@ -2391,7 +2349,7 @@
     </row>
     <row r="8" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="B8" t="s">
         <v>44</v>
@@ -2400,12 +2358,12 @@
         <v>80</v>
       </c>
       <c r="D8" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="E8" t="s">
-        <v>126</v>
-      </c>
-      <c r="F8" s="10" t="s">
+        <v>123</v>
+      </c>
+      <c r="F8" t="s">
         <v>80</v>
       </c>
       <c r="G8" t="s">
@@ -2450,18 +2408,17 @@
     </row>
     <row r="9" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="B9" t="s">
         <v>44</v>
       </c>
       <c r="C9" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="E9" t="s">
         <v>63</v>
       </c>
-      <c r="F9" s="10"/>
       <c r="G9" t="s">
         <v>48</v>
       </c>
@@ -2489,7 +2446,7 @@
     </row>
     <row r="10" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="B10" t="s">
         <v>44</v>
@@ -2498,12 +2455,12 @@
         <v>80</v>
       </c>
       <c r="D10" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="E10" t="s">
-        <v>127</v>
-      </c>
-      <c r="F10" s="10" t="s">
+        <v>124</v>
+      </c>
+      <c r="F10" t="s">
         <v>80</v>
       </c>
       <c r="G10" t="s">
@@ -2548,18 +2505,17 @@
     </row>
     <row r="11" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="B11" t="s">
         <v>44</v>
       </c>
       <c r="C11" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="E11" t="s">
         <v>63</v>
       </c>
-      <c r="F11" s="10"/>
       <c r="G11" t="s">
         <v>48</v>
       </c>
@@ -2817,7 +2773,7 @@
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
     </row>
   </sheetData>

--- a/Spine_Projects/01_input_data/01_input_raw/Products/jet_fuel/Model_Data_Base_jet_fuel.xlsx
+++ b/Spine_Projects/01_input_data/01_input_raw/Products/jet_fuel/Model_Data_Base_jet_fuel.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kar.eco\Documents\GitHub\Nord_H2ub\Spine_Projects\01_input_data\01_input_raw\Products\jet_fuel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jfg.eco\Documents\GitHub\Nord_H2ub\Spine_Projects\01_input_data\01_input_raw\Products\jet_fuel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2224631A-0689-4B3D-A1E5-2107ECC324E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{71B317FE-C3C0-4400-8A48-3307C77295A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" activeTab="4" xr2:uid="{50334894-9481-4F8E-BD29-206032E10C62}"/>
+    <workbookView xWindow="-10110" yWindow="-21720" windowWidth="51840" windowHeight="21120" activeTab="2" xr2:uid="{50334894-9481-4F8E-BD29-206032E10C62}"/>
   </bookViews>
   <sheets>
     <sheet name="Units" sheetId="1" r:id="rId1"/>
@@ -53,7 +53,7 @@
     <definedName name="IQ_YTD">3000</definedName>
     <definedName name="IQ_YTDMONTH" hidden="1">130000</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" concurrentManualCount="6"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -74,7 +74,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="264" uniqueCount="133">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="258" uniqueCount="130">
   <si>
     <t>Unit</t>
   </si>
@@ -325,12 +325,6 @@
     <t>h2_st</t>
   </si>
   <si>
-    <t>pl_dh</t>
-  </si>
-  <si>
-    <t>dh</t>
-  </si>
-  <si>
     <t>jet_fuel_st</t>
   </si>
   <si>
@@ -470,9 +464,6 @@
   </si>
   <si>
     <t>excess_heat</t>
-  </si>
-  <si>
-    <t>heat</t>
   </si>
 </sst>
 </file>
@@ -579,6 +570,17 @@
   </cellStyles>
   <dxfs count="19">
     <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
       <border diagonalUp="0" diagonalDown="0">
         <left/>
         <right/>
@@ -675,17 +677,6 @@
         <vertical/>
         <horizontal/>
       </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
     </dxf>
     <dxf>
       <border diagonalUp="0" diagonalDown="0">
@@ -851,36 +842,36 @@
   <tableColumns count="17">
     <tableColumn id="1" xr3:uid="{CD5761E6-0259-4D3B-B945-2F2B9275A761}" name="Unit"/>
     <tableColumn id="2" xr3:uid="{8206E937-98CA-48B8-8ECF-A8CC8CEA0E7A}" name="Object_type"/>
-    <tableColumn id="3" xr3:uid="{25658B53-E729-4F77-A87A-2C1AA31D180F}" name="Input1" dataDxfId="6"/>
-    <tableColumn id="4" xr3:uid="{C20E16FC-DEE5-46FF-98E7-EC2B1178D89F}" name="Input2" dataDxfId="5"/>
-    <tableColumn id="13" xr3:uid="{C4257F9B-BEBE-4928-A299-FA13BAF91F57}" name="Input3" dataDxfId="4"/>
-    <tableColumn id="14" xr3:uid="{E33FDA0D-66C9-4616-8A81-6F5E0E166ED4}" name="Input4" dataDxfId="3"/>
-    <tableColumn id="5" xr3:uid="{901F195D-0BA8-4EDC-88F0-75A5DF763740}" name="Output1" dataDxfId="2"/>
-    <tableColumn id="6" xr3:uid="{0D5DCA48-4EAB-497A-B34F-5091694CCF48}" name="Output2" dataDxfId="1"/>
-    <tableColumn id="15" xr3:uid="{E758FC30-F120-4234-A984-DD9BB9F5CBE5}" name="Output3" dataDxfId="0"/>
-    <tableColumn id="16" xr3:uid="{85570B5D-60DB-4C61-80EB-881EDB346388}" name="Output4" dataDxfId="16"/>
-    <tableColumn id="10" xr3:uid="{40961C24-C288-48FE-96C9-C696058F1146}" name="Relation_In1_In2" dataDxfId="15"/>
-    <tableColumn id="7" xr3:uid="{E93572D0-6388-4D7C-A2BF-3805225F4F50}" name="Relation_In1_In3" dataDxfId="14"/>
-    <tableColumn id="8" xr3:uid="{BAF59A78-842A-475C-B900-52E45F0F2C02}" name="Relation_In1_In4" dataDxfId="13"/>
-    <tableColumn id="11" xr3:uid="{63A0B53D-07BC-4C95-B97C-243557E4A128}" name="Relation_In1_Out1" dataDxfId="12"/>
-    <tableColumn id="25" xr3:uid="{44B35FDD-04C5-401A-9765-766FCD023027}" name="Relation_Out1_Out2" dataDxfId="11"/>
-    <tableColumn id="9" xr3:uid="{3E00680F-559F-4DED-989F-C435D3C0AEC7}" name="Relation_Out1_Out3" dataDxfId="10"/>
-    <tableColumn id="12" xr3:uid="{17E13652-ACBE-480B-A89B-1AB97BFEAE60}" name="Relation_Out1_Out4" dataDxfId="9"/>
+    <tableColumn id="3" xr3:uid="{25658B53-E729-4F77-A87A-2C1AA31D180F}" name="Input1" dataDxfId="16"/>
+    <tableColumn id="4" xr3:uid="{C20E16FC-DEE5-46FF-98E7-EC2B1178D89F}" name="Input2" dataDxfId="15"/>
+    <tableColumn id="13" xr3:uid="{C4257F9B-BEBE-4928-A299-FA13BAF91F57}" name="Input3" dataDxfId="14"/>
+    <tableColumn id="14" xr3:uid="{E33FDA0D-66C9-4616-8A81-6F5E0E166ED4}" name="Input4" dataDxfId="13"/>
+    <tableColumn id="5" xr3:uid="{901F195D-0BA8-4EDC-88F0-75A5DF763740}" name="Output1" dataDxfId="12"/>
+    <tableColumn id="6" xr3:uid="{0D5DCA48-4EAB-497A-B34F-5091694CCF48}" name="Output2" dataDxfId="11"/>
+    <tableColumn id="15" xr3:uid="{E758FC30-F120-4234-A984-DD9BB9F5CBE5}" name="Output3" dataDxfId="10"/>
+    <tableColumn id="16" xr3:uid="{85570B5D-60DB-4C61-80EB-881EDB346388}" name="Output4" dataDxfId="9"/>
+    <tableColumn id="10" xr3:uid="{40961C24-C288-48FE-96C9-C696058F1146}" name="Relation_In1_In2" dataDxfId="8"/>
+    <tableColumn id="7" xr3:uid="{E93572D0-6388-4D7C-A2BF-3805225F4F50}" name="Relation_In1_In3" dataDxfId="7"/>
+    <tableColumn id="8" xr3:uid="{BAF59A78-842A-475C-B900-52E45F0F2C02}" name="Relation_In1_In4" dataDxfId="6"/>
+    <tableColumn id="11" xr3:uid="{63A0B53D-07BC-4C95-B97C-243557E4A128}" name="Relation_In1_Out1" dataDxfId="5"/>
+    <tableColumn id="25" xr3:uid="{44B35FDD-04C5-401A-9765-766FCD023027}" name="Relation_Out1_Out2" dataDxfId="4"/>
+    <tableColumn id="9" xr3:uid="{3E00680F-559F-4DED-989F-C435D3C0AEC7}" name="Relation_Out1_Out3" dataDxfId="3"/>
+    <tableColumn id="12" xr3:uid="{17E13652-ACBE-480B-A89B-1AB97BFEAE60}" name="Relation_Out1_Out4" dataDxfId="2"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{EFFB7C99-360E-4E9C-9C4B-24063303FF25}" name="Table13" displayName="Table13" ref="A1:AA11" totalsRowShown="0">
-  <autoFilter ref="A1:AA11" xr:uid="{EFFB7C99-360E-4E9C-9C4B-24063303FF25}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{EFFB7C99-360E-4E9C-9C4B-24063303FF25}" name="Table13" displayName="Table13" ref="A1:AA10" totalsRowShown="0">
+  <autoFilter ref="A1:AA10" xr:uid="{EFFB7C99-360E-4E9C-9C4B-24063303FF25}"/>
   <tableColumns count="27">
     <tableColumn id="1" xr3:uid="{0B60459B-BFAA-433A-998B-57564CCEFAF1}" name="Connection"/>
     <tableColumn id="2" xr3:uid="{C0C61C1C-8F08-418C-94F7-C2BD6112A62E}" name="Object_type"/>
     <tableColumn id="3" xr3:uid="{BC9D86F7-8FDE-4FAF-A6B2-8BF7829723EF}" name="Input1"/>
     <tableColumn id="4" xr3:uid="{31F6D71E-306D-4146-A535-A6A629EBE2DC}" name="Input2"/>
     <tableColumn id="5" xr3:uid="{E176ABAF-D150-4E6A-8921-E24FCEB64CEB}" name="Output1"/>
-    <tableColumn id="22" xr3:uid="{EB53F534-595A-4E1E-82EE-E811ECDB4974}" name="Output2" dataDxfId="8"/>
+    <tableColumn id="22" xr3:uid="{EB53F534-595A-4E1E-82EE-E811ECDB4974}" name="Output2" dataDxfId="1"/>
     <tableColumn id="6" xr3:uid="{C9818184-D13F-4AF4-AE3A-C64F072A0385}" name="Connection_type"/>
     <tableColumn id="15" xr3:uid="{52C8ADC6-49B2-4339-A761-5E82E904E3A6}" name="Cap_Input1_existing"/>
     <tableColumn id="14" xr3:uid="{F6461E15-EE92-48B4-8879-9BDE3EBAAA17}" name="Cap_Input1_max"/>
@@ -911,7 +902,7 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{070C7B69-9214-47B9-93F0-C6C6118ED7CC}" name="Table134" displayName="Table134" ref="A1:K5" totalsRowShown="0">
   <autoFilter ref="A1:K5" xr:uid="{070C7B69-9214-47B9-93F0-C6C6118ED7CC}"/>
   <tableColumns count="11">
-    <tableColumn id="1" xr3:uid="{59CF1CEF-E7FA-4B7F-9443-D4A6EAAB7A8F}" name="Storage" dataDxfId="7"/>
+    <tableColumn id="1" xr3:uid="{59CF1CEF-E7FA-4B7F-9443-D4A6EAAB7A8F}" name="Storage" dataDxfId="0"/>
     <tableColumn id="4" xr3:uid="{AEAA1B51-84C1-491F-81D5-7757B30BDCCD}" name="Object_type"/>
     <tableColumn id="6" xr3:uid="{FA5F8582-61FC-4A96-9E8D-E08E92F1962D}" name="value_before"/>
     <tableColumn id="2" xr3:uid="{1FB70133-79C8-41A8-BCD5-AC8AA5856E5B}" name="has_state"/>
@@ -1238,29 +1229,29 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{576C757C-091A-46DF-949E-B17661031FDE}">
   <dimension ref="A1:R13"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="15.85546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="20.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="25.7109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="18.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="15.88671875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="20.5546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="25.6640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="18.109375" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="18" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="11.140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.85546875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="15.85546875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="18.42578125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="15.140625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="17.85546875" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="15.7109375" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="11.42578125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="11.7109375" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="21.140625" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="19.7109375" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="10.5703125" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="17.28515625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.88671875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15.88671875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="18.44140625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="15.109375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="17.88671875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="15.6640625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="11.44140625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="11.6640625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="21.109375" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="19.6640625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="10.5546875" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="17.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1268,7 +1259,7 @@
         <v>34</v>
       </c>
       <c r="C1" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="D1" t="s">
         <v>36</v>
@@ -1277,22 +1268,22 @@
         <v>33</v>
       </c>
       <c r="F1" t="s">
+        <v>107</v>
+      </c>
+      <c r="G1" t="s">
+        <v>108</v>
+      </c>
+      <c r="H1" t="s">
         <v>109</v>
       </c>
-      <c r="G1" t="s">
+      <c r="I1" t="s">
         <v>110</v>
       </c>
-      <c r="H1" t="s">
-        <v>111</v>
-      </c>
-      <c r="I1" t="s">
-        <v>112</v>
-      </c>
       <c r="J1" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="K1" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="L1" t="s">
         <v>37</v>
@@ -1304,7 +1295,7 @@
         <v>27</v>
       </c>
       <c r="O1" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="P1" t="s">
         <v>38</v>
@@ -1313,10 +1304,10 @@
         <v>39</v>
       </c>
       <c r="R1" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="2" spans="1:18" x14ac:dyDescent="0.25">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="2" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>62</v>
       </c>
@@ -1324,38 +1315,38 @@
         <v>41</v>
       </c>
       <c r="C2" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="P2" s="1"/>
       <c r="Q2" s="1"/>
     </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="B3" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="C3" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="P3" s="1"/>
       <c r="Q3" s="1"/>
     </row>
-    <row r="4" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="B4" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="C4" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="P4" s="1"/>
       <c r="Q4" s="1"/>
     </row>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>64</v>
       </c>
@@ -1377,7 +1368,7 @@
       <c r="P5" s="1"/>
       <c r="Q5" s="1"/>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>67</v>
       </c>
@@ -1390,7 +1381,7 @@
       <c r="P6" s="1"/>
       <c r="Q6" s="1"/>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>75</v>
       </c>
@@ -1403,7 +1394,7 @@
       <c r="P7" s="1"/>
       <c r="Q7" s="1"/>
     </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A8" s="4" t="s">
         <v>70</v>
       </c>
@@ -1416,9 +1407,9 @@
       <c r="P8" s="1"/>
       <c r="Q8" s="1"/>
     </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="B9" t="s">
         <v>42</v>
@@ -1432,7 +1423,7 @@
       <c r="P9" s="1"/>
       <c r="Q9" s="1"/>
     </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A10" s="4" t="s">
         <v>73</v>
       </c>
@@ -1443,7 +1434,7 @@
         <v>74</v>
       </c>
       <c r="E10" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="P10" s="1"/>
       <c r="Q10" s="1"/>
@@ -1451,12 +1442,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="B11" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="C11" t="s">
         <v>65</v>
@@ -1464,12 +1455,12 @@
       <c r="P11" s="1"/>
       <c r="Q11" s="1"/>
     </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="B12" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="C12" t="s">
         <v>68</v>
@@ -1477,12 +1468,12 @@
       <c r="P12" s="1"/>
       <c r="Q12" s="1"/>
     </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="B13" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="C13" t="s">
         <v>63</v>
@@ -1505,23 +1496,23 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8478C130-C296-4571-ABF4-62E91E9E2767}">
   <dimension ref="A1:Q13"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="15.85546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="20.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.28515625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.85546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="15.88671875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="20.5546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.33203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.88671875" bestFit="1" customWidth="1"/>
     <col min="5" max="6" width="9" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="25.7109375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.28515625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="11.85546875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="10.5703125" bestFit="1" customWidth="1"/>
-    <col min="11" max="13" width="18.28515625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="25.6640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.33203125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="11.88671875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="10.5546875" bestFit="1" customWidth="1"/>
+    <col min="11" max="13" width="18.33203125" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="20" bestFit="1" customWidth="1"/>
-    <col min="15" max="17" width="21.5703125" bestFit="1" customWidth="1"/>
+    <col min="15" max="17" width="21.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1535,10 +1526,10 @@
         <v>2</v>
       </c>
       <c r="E1" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="F1" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="G1" t="s">
         <v>3</v>
@@ -1547,34 +1538,34 @@
         <v>4</v>
       </c>
       <c r="I1" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="J1" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="K1" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="L1" t="s">
+        <v>113</v>
+      </c>
+      <c r="M1" t="s">
+        <v>114</v>
+      </c>
+      <c r="N1" t="s">
+        <v>117</v>
+      </c>
+      <c r="O1" t="s">
+        <v>100</v>
+      </c>
+      <c r="P1" t="s">
         <v>115</v>
       </c>
-      <c r="M1" t="s">
+      <c r="Q1" t="s">
         <v>116</v>
       </c>
-      <c r="N1" t="s">
-        <v>119</v>
-      </c>
-      <c r="O1" t="s">
-        <v>102</v>
-      </c>
-      <c r="P1" t="s">
-        <v>117</v>
-      </c>
-      <c r="Q1" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
+    </row>
+    <row r="2" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>62</v>
       </c>
@@ -1586,7 +1577,7 @@
       <c r="E2" s="2"/>
       <c r="F2" s="2"/>
       <c r="G2" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="H2" s="2"/>
       <c r="I2" s="5"/>
@@ -1599,19 +1590,19 @@
       <c r="P2" s="5"/>
       <c r="Q2" s="5"/>
     </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="C3" s="3"/>
       <c r="D3" s="3"/>
       <c r="E3" s="3"/>
       <c r="F3" s="3"/>
       <c r="G3" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="H3" s="3"/>
       <c r="I3" s="3"/>
@@ -1624,19 +1615,19 @@
       <c r="P3" s="3"/>
       <c r="Q3" s="3"/>
     </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="B4" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" s="2"/>
       <c r="E4" s="2"/>
       <c r="F4" s="2"/>
       <c r="G4" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="H4" s="2"/>
       <c r="I4" s="2"/>
@@ -1649,7 +1640,7 @@
       <c r="P4" s="2"/>
       <c r="Q4" s="2"/>
     </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A5" s="3" t="s">
         <v>64</v>
       </c>
@@ -1668,7 +1659,7 @@
         <v>66</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="I5" s="3"/>
       <c r="J5" s="3"/>
@@ -1684,7 +1675,7 @@
       <c r="P5" s="3"/>
       <c r="Q5" s="3"/>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
         <v>67</v>
       </c>
@@ -1717,7 +1708,7 @@
       <c r="P6" s="2"/>
       <c r="Q6" s="2"/>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>75</v>
       </c>
@@ -1754,7 +1745,7 @@
       <c r="P7" s="3"/>
       <c r="Q7" s="3"/>
     </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>70</v>
       </c>
@@ -1795,15 +1786,15 @@
       <c r="P8" s="2"/>
       <c r="Q8" s="2"/>
     </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="B9" t="s">
         <v>42</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="D9" s="3" t="s">
         <v>65</v>
@@ -1828,15 +1819,15 @@
       <c r="P9" s="3"/>
       <c r="Q9" s="3"/>
     </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
+        <v>96</v>
+      </c>
+      <c r="B10" t="s">
+        <v>90</v>
+      </c>
+      <c r="C10" s="3" t="s">
         <v>98</v>
-      </c>
-      <c r="B10" t="s">
-        <v>92</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>100</v>
       </c>
       <c r="G10" s="3" t="s">
         <v>65</v>
@@ -1845,15 +1836,15 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
+        <v>97</v>
+      </c>
+      <c r="B11" t="s">
+        <v>90</v>
+      </c>
+      <c r="C11" s="3" t="s">
         <v>99</v>
-      </c>
-      <c r="B11" t="s">
-        <v>92</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>101</v>
       </c>
       <c r="D11" s="3"/>
       <c r="E11" s="3"/>
@@ -1874,7 +1865,7 @@
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
     </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>73</v>
       </c>
@@ -1898,7 +1889,7 @@
         <v>65</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="J12" s="2"/>
       <c r="K12" s="6">
@@ -1919,12 +1910,12 @@
       </c>
       <c r="Q12" s="6"/>
     </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="B13" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="C13" s="3" t="s">
         <v>63</v>
@@ -1933,7 +1924,7 @@
       <c r="E13" s="3"/>
       <c r="F13" s="3"/>
       <c r="G13" s="3" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="H13" s="3"/>
       <c r="I13" s="3"/>
@@ -1960,35 +1951,35 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C870BDA0-9E4C-481D-87BE-9D47789809C8}">
-  <dimension ref="A1:AA11"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:AA10"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="27.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="18.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="5" width="25.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="27.44140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="5" width="25.6640625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="17" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="36.85546875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="20.7109375" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="17.42578125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="20.7109375" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="17.42578125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="22.140625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="19.140625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="22.140625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="19.140625" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="10.85546875" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="15.5703125" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="17.140625" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="18.85546875" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="17.140625" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="11.85546875" bestFit="1" customWidth="1"/>
-    <col min="22" max="23" width="17.85546875" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="19.42578125" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="36.5703125" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="24.28515625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="36.88671875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="20.6640625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="17.44140625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="20.6640625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="17.44140625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="22.109375" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="19.109375" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="22.109375" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="19.109375" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="10.88671875" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="15.5546875" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="17.109375" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="18.88671875" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="17.109375" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="11.88671875" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="17.88671875" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="19.44140625" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="36.5546875" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="24.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>15</v>
       </c>
@@ -2068,10 +2059,10 @@
         <v>35</v>
       </c>
       <c r="AA1" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="2" spans="1:27" x14ac:dyDescent="0.25">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="2" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>79</v>
       </c>
@@ -2130,7 +2121,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>81</v>
       </c>
@@ -2186,9 +2177,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A4" s="4" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="B4" t="s">
         <v>61</v>
@@ -2197,10 +2188,10 @@
         <v>78</v>
       </c>
       <c r="D4" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="E4" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="F4" t="s">
         <v>78</v>
@@ -2212,18 +2203,24 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>83</v>
+        <v>123</v>
       </c>
       <c r="B5" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="C5" t="s">
-        <v>132</v>
+        <v>80</v>
+      </c>
+      <c r="D5" t="s">
+        <v>120</v>
       </c>
       <c r="E5" t="s">
-        <v>84</v>
+        <v>120</v>
+      </c>
+      <c r="F5" t="s">
+        <v>80</v>
       </c>
       <c r="G5" t="s">
         <v>48</v>
@@ -2234,11 +2231,26 @@
       <c r="I5">
         <v>1000</v>
       </c>
+      <c r="J5">
+        <v>1000</v>
+      </c>
+      <c r="K5">
+        <v>1000</v>
+      </c>
       <c r="L5">
         <v>1000</v>
       </c>
       <c r="M5">
         <v>1000</v>
+      </c>
+      <c r="N5">
+        <v>1000</v>
+      </c>
+      <c r="O5">
+        <v>1000</v>
+      </c>
+      <c r="R5">
+        <v>1</v>
       </c>
       <c r="T5">
         <v>1</v>
@@ -2250,24 +2262,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B6" t="s">
         <v>44</v>
       </c>
       <c r="C6" t="s">
-        <v>80</v>
-      </c>
-      <c r="D6" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="E6" t="s">
-        <v>122</v>
-      </c>
-      <c r="F6" t="s">
-        <v>80</v>
+        <v>63</v>
       </c>
       <c r="G6" t="s">
         <v>48</v>
@@ -2278,26 +2284,11 @@
       <c r="I6">
         <v>1000</v>
       </c>
-      <c r="J6">
-        <v>1000</v>
-      </c>
-      <c r="K6">
-        <v>1000</v>
-      </c>
       <c r="L6">
         <v>1000</v>
       </c>
       <c r="M6">
         <v>1000</v>
-      </c>
-      <c r="N6">
-        <v>1000</v>
-      </c>
-      <c r="O6">
-        <v>1000</v>
-      </c>
-      <c r="R6">
-        <v>1</v>
       </c>
       <c r="T6">
         <v>1</v>
@@ -2309,18 +2300,24 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B7" t="s">
         <v>44</v>
       </c>
       <c r="C7" t="s">
-        <v>122</v>
+        <v>80</v>
+      </c>
+      <c r="D7" t="s">
+        <v>121</v>
       </c>
       <c r="E7" t="s">
-        <v>63</v>
+        <v>121</v>
+      </c>
+      <c r="F7" t="s">
+        <v>80</v>
       </c>
       <c r="G7" t="s">
         <v>48</v>
@@ -2331,11 +2328,26 @@
       <c r="I7">
         <v>1000</v>
       </c>
+      <c r="J7">
+        <v>1000</v>
+      </c>
+      <c r="K7">
+        <v>1000</v>
+      </c>
       <c r="L7">
         <v>1000</v>
       </c>
       <c r="M7">
         <v>1000</v>
+      </c>
+      <c r="N7">
+        <v>1000</v>
+      </c>
+      <c r="O7">
+        <v>1000</v>
+      </c>
+      <c r="R7">
+        <v>1</v>
       </c>
       <c r="T7">
         <v>1</v>
@@ -2347,24 +2359,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B8" t="s">
         <v>44</v>
       </c>
       <c r="C8" t="s">
-        <v>80</v>
-      </c>
-      <c r="D8" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="E8" t="s">
-        <v>123</v>
-      </c>
-      <c r="F8" t="s">
-        <v>80</v>
+        <v>63</v>
       </c>
       <c r="G8" t="s">
         <v>48</v>
@@ -2375,26 +2381,11 @@
       <c r="I8">
         <v>1000</v>
       </c>
-      <c r="J8">
-        <v>1000</v>
-      </c>
-      <c r="K8">
-        <v>1000</v>
-      </c>
       <c r="L8">
         <v>1000</v>
       </c>
       <c r="M8">
         <v>1000</v>
-      </c>
-      <c r="N8">
-        <v>1000</v>
-      </c>
-      <c r="O8">
-        <v>1000</v>
-      </c>
-      <c r="R8">
-        <v>1</v>
       </c>
       <c r="T8">
         <v>1</v>
@@ -2406,18 +2397,24 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B9" t="s">
         <v>44</v>
       </c>
       <c r="C9" t="s">
-        <v>123</v>
+        <v>80</v>
+      </c>
+      <c r="D9" t="s">
+        <v>122</v>
       </c>
       <c r="E9" t="s">
-        <v>63</v>
+        <v>122</v>
+      </c>
+      <c r="F9" t="s">
+        <v>80</v>
       </c>
       <c r="G9" t="s">
         <v>48</v>
@@ -2428,11 +2425,26 @@
       <c r="I9">
         <v>1000</v>
       </c>
+      <c r="J9">
+        <v>1000</v>
+      </c>
+      <c r="K9">
+        <v>1000</v>
+      </c>
       <c r="L9">
         <v>1000</v>
       </c>
       <c r="M9">
         <v>1000</v>
+      </c>
+      <c r="N9">
+        <v>1000</v>
+      </c>
+      <c r="O9">
+        <v>1000</v>
+      </c>
+      <c r="R9">
+        <v>1</v>
       </c>
       <c r="T9">
         <v>1</v>
@@ -2444,24 +2456,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B10" t="s">
         <v>44</v>
       </c>
       <c r="C10" t="s">
-        <v>80</v>
-      </c>
-      <c r="D10" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="E10" t="s">
-        <v>124</v>
-      </c>
-      <c r="F10" t="s">
-        <v>80</v>
+        <v>63</v>
       </c>
       <c r="G10" t="s">
         <v>48</v>
@@ -2472,26 +2478,11 @@
       <c r="I10">
         <v>1000</v>
       </c>
-      <c r="J10">
-        <v>1000</v>
-      </c>
-      <c r="K10">
-        <v>1000</v>
-      </c>
       <c r="L10">
         <v>1000</v>
       </c>
       <c r="M10">
         <v>1000</v>
-      </c>
-      <c r="N10">
-        <v>1000</v>
-      </c>
-      <c r="O10">
-        <v>1000</v>
-      </c>
-      <c r="R10">
-        <v>1</v>
       </c>
       <c r="T10">
         <v>1</v>
@@ -2500,44 +2491,6 @@
         <v>46</v>
       </c>
       <c r="AA10">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>130</v>
-      </c>
-      <c r="B11" t="s">
-        <v>44</v>
-      </c>
-      <c r="C11" t="s">
-        <v>124</v>
-      </c>
-      <c r="E11" t="s">
-        <v>63</v>
-      </c>
-      <c r="G11" t="s">
-        <v>48</v>
-      </c>
-      <c r="H11">
-        <v>1000</v>
-      </c>
-      <c r="I11">
-        <v>1000</v>
-      </c>
-      <c r="L11">
-        <v>1000</v>
-      </c>
-      <c r="M11">
-        <v>1000</v>
-      </c>
-      <c r="T11">
-        <v>1</v>
-      </c>
-      <c r="Z11" t="s">
-        <v>46</v>
-      </c>
-      <c r="AA11">
         <v>1</v>
       </c>
     </row>
@@ -2553,20 +2506,20 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{981CFA5E-60F3-446F-A856-2FA65B76879A}">
   <dimension ref="A1:K3"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="10.140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.5703125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="16.5703125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="15.85546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="15.85546875" customWidth="1"/>
+    <col min="1" max="1" width="10.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.5546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.5546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="16.5546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15.88671875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="15.88671875" customWidth="1"/>
     <col min="7" max="7" width="9" customWidth="1"/>
     <col min="8" max="8" width="11" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="11.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>19</v>
       </c>
@@ -2598,10 +2551,10 @@
         <v>27</v>
       </c>
       <c r="K1" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>82</v>
       </c>
@@ -2627,9 +2580,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="B3" t="s">
         <v>60</v>
@@ -2676,104 +2629,104 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4F682EA3-CCEB-45E2-AC25-979810840C6C}">
   <dimension ref="A1:A19"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="19.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="19.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
     </row>
   </sheetData>
